--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92452</v>
+        <v>92455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92455</v>
+        <v>92456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92461</v>
+        <v>92463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
